--- a/temp/espc-2/searchByMAC.xlsx
+++ b/temp/espc-2/searchByMAC.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="42">
   <si>
     <t>ЭСПЦ-2</t>
   </si>
@@ -134,6 +134,12 @@
   </si>
   <si>
     <t>17.48</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
 </sst>
 </file>
@@ -490,7 +496,7 @@
     <col min="1" max="44" width="5.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -510,25 +516,34 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="F2" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
+      <c r="N2" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>1</v>
@@ -548,7 +563,7 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
@@ -570,7 +585,7 @@
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
@@ -592,7 +607,7 @@
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
@@ -614,7 +629,7 @@
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
@@ -636,7 +651,7 @@
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
@@ -658,7 +673,7 @@
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
@@ -680,7 +695,7 @@
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
@@ -702,7 +717,7 @@
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
@@ -724,7 +739,7 @@
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
@@ -746,7 +761,7 @@
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
@@ -768,7 +783,7 @@
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
@@ -790,7 +805,7 @@
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
@@ -812,7 +827,7 @@
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">

--- a/temp/espc-2/searchByMAC.xlsx
+++ b/temp/espc-2/searchByMAC.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="47">
   <si>
     <t>ЭСПЦ-2</t>
   </si>
@@ -140,6 +140,21 @@
   </si>
   <si>
     <t>3</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>6.2.17</t>
+  </si>
+  <si>
+    <t>6.2.16</t>
+  </si>
+  <si>
+    <t>6.2.23</t>
+  </si>
+  <si>
+    <t>6.2.22</t>
   </si>
 </sst>
 </file>
@@ -490,13 +505,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T211"/>
+  <dimension ref="A1:AC211"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="44" width="5.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -516,7 +531,7 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -543,7 +558,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>1</v>
@@ -563,7 +578,7 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
@@ -573,19 +588,31 @@
         <v>3</v>
       </c>
       <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
+      <c r="F4" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
+      <c r="J4" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
+      <c r="N4" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S4">
+        <v>3</v>
+      </c>
+      <c r="Y4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
@@ -596,18 +623,45 @@
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
+      <c r="K5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q5" s="1"/>
+      <c r="T5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="V5" s="1"/>
+      <c r="Z5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB5" s="1"/>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
@@ -618,18 +672,45 @@
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q6" s="1"/>
+      <c r="T6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="V6" s="1"/>
+      <c r="Z6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB6" s="1"/>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
@@ -640,18 +721,45 @@
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
+      <c r="K7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q7" s="1"/>
+      <c r="T7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="V7" s="1"/>
+      <c r="Z7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB7" s="1"/>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
@@ -662,18 +770,45 @@
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
+      <c r="G8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
+      <c r="K8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q8" s="1"/>
+      <c r="T8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V8" s="1"/>
+      <c r="Z8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB8" s="1"/>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
@@ -688,14 +823,37 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="1"/>
+      <c r="K9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q9" s="1"/>
+      <c r="T9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="V9" s="1"/>
+      <c r="Z9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB9" s="1"/>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
@@ -714,10 +872,38 @@
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y10">
+        <v>11</v>
+      </c>
+      <c r="Z10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
@@ -737,9 +923,28 @@
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="P11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z11" s="1"/>
+      <c r="AA11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB11" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
@@ -760,8 +965,39 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S12">
+        <v>1</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="X12" s="1"/>
+      <c r="Y12">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC12" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
@@ -782,8 +1018,34 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="T13" s="1"/>
+      <c r="U13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X13" s="1"/>
+      <c r="Y13">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC13" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
@@ -805,7 +1067,7 @@
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
@@ -826,8 +1088,14 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S15">
+        <v>3</v>
+      </c>
+      <c r="Y15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
@@ -848,8 +1116,22 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="T16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="V16" s="1"/>
+      <c r="Z16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB16" s="1"/>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -866,8 +1148,22 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="T17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="V17" s="1"/>
+      <c r="Z17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB17" s="1"/>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
         <v>8</v>
@@ -886,8 +1182,22 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="T18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="V18" s="1"/>
+      <c r="Z18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB18" s="1"/>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
@@ -908,8 +1218,22 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="T19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V19" s="1"/>
+      <c r="Z19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB19" s="1"/>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
@@ -930,8 +1254,22 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="T20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="V20" s="1"/>
+      <c r="Z20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB20" s="1"/>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
@@ -952,8 +1290,20 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="T21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="V21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z21" s="1"/>
+      <c r="AA21" s="1"/>
+      <c r="AB21" s="1"/>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1" t="s">
@@ -974,8 +1324,22 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="T22" s="1"/>
+      <c r="U22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="V22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z22" s="1"/>
+      <c r="AA22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB22" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
@@ -996,8 +1360,16 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+      <c r="V23" s="1"/>
+      <c r="W23" s="1"/>
+      <c r="Z23" s="1"/>
+      <c r="AA23" s="1"/>
+      <c r="AB23" s="1"/>
+      <c r="AC23" s="1"/>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
@@ -1018,8 +1390,22 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="T24" s="1"/>
+      <c r="U24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z24" s="1"/>
+      <c r="AA24" s="1"/>
+      <c r="AB24" s="1"/>
+      <c r="AC24" s="1"/>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
@@ -1041,7 +1427,7 @@
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1" t="s">
@@ -1063,7 +1449,7 @@
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1" t="s">
@@ -1085,7 +1471,7 @@
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1" t="s">
@@ -1107,7 +1493,7 @@
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1" t="s">
@@ -1129,7 +1515,7 @@
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
@@ -1151,7 +1537,7 @@
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
@@ -1173,7 +1559,7 @@
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>

--- a/temp/espc-2/searchByMAC.xlsx
+++ b/temp/espc-2/searchByMAC.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView minimized="1" xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>

--- a/temp/espc-2/searchByMAC.xlsx
+++ b/temp/espc-2/searchByMAC.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="47">
   <si>
     <t>ЭСПЦ-2</t>
   </si>
@@ -197,10 +197,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -505,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC211"/>
+  <dimension ref="A1:AS211"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="44" width="5.7109375" customWidth="1"/>
@@ -863,11 +864,6 @@
         <v>11</v>
       </c>
       <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -913,11 +909,6 @@
         <v>3</v>
       </c>
       <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -1131,7 +1122,7 @@
       </c>
       <c r="AB16" s="1"/>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1163,7 +1154,7 @@
       </c>
       <c r="AB17" s="1"/>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
         <v>8</v>
@@ -1197,7 +1188,7 @@
       </c>
       <c r="AB18" s="1"/>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
@@ -1233,7 +1224,7 @@
       </c>
       <c r="AB19" s="1"/>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
@@ -1269,7 +1260,7 @@
       </c>
       <c r="AB20" s="1"/>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
@@ -1303,7 +1294,7 @@
       <c r="AA21" s="1"/>
       <c r="AB21" s="1"/>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1" t="s">
@@ -1339,7 +1330,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
@@ -1369,7 +1360,7 @@
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
@@ -1405,7 +1396,7 @@
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
@@ -1427,7 +1418,7 @@
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1" t="s">
@@ -1449,7 +1440,7 @@
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1" t="s">
@@ -1470,8 +1461,34 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
-    </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="S27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="1"/>
+      <c r="W27" s="2"/>
+      <c r="Y27">
+        <v>1</v>
+      </c>
+      <c r="AF27" s="1">
+        <v>2</v>
+      </c>
+      <c r="AG27" s="1"/>
+      <c r="AH27" s="1"/>
+      <c r="AI27" s="1"/>
+      <c r="AJ27" s="1"/>
+      <c r="AK27" s="1"/>
+      <c r="AL27" s="1"/>
+      <c r="AM27" s="1"/>
+      <c r="AN27" s="1"/>
+      <c r="AO27" s="1"/>
+      <c r="AP27" s="1"/>
+      <c r="AQ27" s="1"/>
+      <c r="AR27" s="1"/>
+      <c r="AS27" s="1"/>
+    </row>
+    <row r="28" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1" t="s">
@@ -1492,8 +1509,55 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
-    </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="S28" s="1"/>
+      <c r="T28" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="V28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z28">
+        <v>17</v>
+      </c>
+      <c r="AB28" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF28" s="1"/>
+      <c r="AG28" s="1">
+        <v>17</v>
+      </c>
+      <c r="AH28" s="1"/>
+      <c r="AI28" s="1"/>
+      <c r="AJ28" s="1"/>
+      <c r="AK28" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AL28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AM28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN28" s="1"/>
+      <c r="AO28" s="1"/>
+      <c r="AP28" s="1"/>
+      <c r="AQ28" s="1"/>
+      <c r="AR28" s="1"/>
+      <c r="AS28" s="1"/>
+    </row>
+    <row r="29" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1" t="s">
@@ -1514,8 +1578,27 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
-    </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AA29">
+        <v>17</v>
+      </c>
+      <c r="AF29" s="1"/>
+      <c r="AG29" s="1"/>
+      <c r="AH29" s="1">
+        <v>17</v>
+      </c>
+      <c r="AI29" s="1"/>
+      <c r="AJ29" s="1"/>
+      <c r="AK29" s="1"/>
+      <c r="AL29" s="1"/>
+      <c r="AM29" s="1"/>
+      <c r="AN29" s="1"/>
+      <c r="AO29" s="1"/>
+      <c r="AP29" s="1"/>
+      <c r="AQ29" s="1"/>
+      <c r="AR29" s="1"/>
+      <c r="AS29" s="1"/>
+    </row>
+    <row r="30" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
@@ -1536,8 +1619,26 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
-    </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AF30" s="1"/>
+      <c r="AG30" s="1"/>
+      <c r="AH30" s="1"/>
+      <c r="AI30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AK30" s="1"/>
+      <c r="AL30" s="1"/>
+      <c r="AM30" s="1"/>
+      <c r="AN30" s="1"/>
+      <c r="AO30" s="1"/>
+      <c r="AP30" s="1"/>
+      <c r="AQ30" s="1"/>
+      <c r="AR30" s="1"/>
+      <c r="AS30" s="1"/>
+    </row>
+    <row r="31" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
@@ -1558,8 +1659,22 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
-    </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AF31" s="1"/>
+      <c r="AG31" s="1"/>
+      <c r="AH31" s="1"/>
+      <c r="AI31" s="1"/>
+      <c r="AJ31" s="1"/>
+      <c r="AK31" s="1"/>
+      <c r="AL31" s="1"/>
+      <c r="AM31" s="1"/>
+      <c r="AN31" s="1"/>
+      <c r="AO31" s="1"/>
+      <c r="AP31" s="1"/>
+      <c r="AQ31" s="1"/>
+      <c r="AR31" s="1"/>
+      <c r="AS31" s="1"/>
+    </row>
+    <row r="32" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1576,8 +1691,43 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S32" s="1">
+        <v>3</v>
+      </c>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+      <c r="W32" s="1"/>
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1"/>
+      <c r="Z32" s="1"/>
+      <c r="AA32" s="1"/>
+      <c r="AB32" s="1"/>
+      <c r="AC32" s="1"/>
+      <c r="AD32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE32" s="1"/>
+      <c r="AF32" s="1"/>
+      <c r="AG32" s="1"/>
+      <c r="AH32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AI32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AJ32" s="1"/>
+      <c r="AK32" s="1"/>
+      <c r="AL32" s="1"/>
+      <c r="AM32" s="1"/>
+      <c r="AN32" s="1"/>
+      <c r="AO32" s="1"/>
+      <c r="AP32" s="1"/>
+      <c r="AQ32" s="1"/>
+      <c r="AR32" s="1"/>
+      <c r="AS32" s="1"/>
+    </row>
+    <row r="33" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
         <v>17</v>
@@ -1602,8 +1752,51 @@
       </c>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S33" s="1"/>
+      <c r="T33" s="1">
+        <v>17</v>
+      </c>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
+      <c r="W33" s="1"/>
+      <c r="X33" s="1"/>
+      <c r="Y33" s="1"/>
+      <c r="Z33" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB33" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC33" s="1"/>
+      <c r="AD33" s="1"/>
+      <c r="AE33" s="1">
+        <v>17</v>
+      </c>
+      <c r="AF33" s="1"/>
+      <c r="AG33" s="1"/>
+      <c r="AH33" s="1"/>
+      <c r="AI33" s="1"/>
+      <c r="AJ33" s="1"/>
+      <c r="AK33" s="1"/>
+      <c r="AL33" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AM33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN33" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO33" s="1"/>
+      <c r="AP33" s="1"/>
+      <c r="AQ33" s="1"/>
+      <c r="AR33" s="1"/>
+      <c r="AS33" s="1"/>
+    </row>
+    <row r="34" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1" t="s">
@@ -1628,8 +1821,39 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1">
+        <v>17</v>
+      </c>
+      <c r="V34" s="1"/>
+      <c r="W34" s="1"/>
+      <c r="X34" s="1"/>
+      <c r="Y34" s="1"/>
+      <c r="Z34" s="1"/>
+      <c r="AA34" s="1"/>
+      <c r="AB34" s="1"/>
+      <c r="AC34" s="1"/>
+      <c r="AD34" s="1"/>
+      <c r="AE34" s="1"/>
+      <c r="AF34" s="1">
+        <v>17</v>
+      </c>
+      <c r="AG34" s="1"/>
+      <c r="AH34" s="1"/>
+      <c r="AI34" s="1"/>
+      <c r="AJ34" s="1"/>
+      <c r="AK34" s="1"/>
+      <c r="AL34" s="1"/>
+      <c r="AM34" s="1"/>
+      <c r="AN34" s="1"/>
+      <c r="AO34" s="1"/>
+      <c r="AP34" s="1"/>
+      <c r="AQ34" s="1"/>
+      <c r="AR34" s="1"/>
+      <c r="AS34" s="1"/>
+    </row>
+    <row r="35" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1" t="s">
@@ -1654,8 +1878,43 @@
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
+      <c r="U35" s="1"/>
+      <c r="V35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W35" s="1"/>
+      <c r="X35" s="1"/>
+      <c r="Y35" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z35" s="1"/>
+      <c r="AA35" s="1"/>
+      <c r="AB35" s="1"/>
+      <c r="AC35" s="1"/>
+      <c r="AD35" s="1"/>
+      <c r="AE35" s="1"/>
+      <c r="AF35" s="1"/>
+      <c r="AG35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AH35" s="1"/>
+      <c r="AI35" s="1"/>
+      <c r="AJ35" s="1"/>
+      <c r="AK35" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AL35" s="1"/>
+      <c r="AM35" s="1"/>
+      <c r="AN35" s="1"/>
+      <c r="AO35" s="1"/>
+      <c r="AP35" s="1"/>
+      <c r="AQ35" s="1"/>
+      <c r="AR35" s="1"/>
+      <c r="AS35" s="1"/>
+    </row>
+    <row r="36" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1" t="s">
@@ -1680,8 +1939,39 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+      <c r="V36" s="1"/>
+      <c r="W36" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="X36" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y36" s="1"/>
+      <c r="Z36" s="1"/>
+      <c r="AA36" s="1"/>
+      <c r="AB36" s="1"/>
+      <c r="AC36" s="1"/>
+      <c r="AD36" s="1"/>
+      <c r="AE36" s="1"/>
+      <c r="AF36" s="1"/>
+      <c r="AG36" s="1"/>
+      <c r="AH36" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI36" s="1"/>
+      <c r="AJ36" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AK36" s="1"/>
+      <c r="AL36" s="1"/>
+      <c r="AM36" s="1"/>
+      <c r="AN36" s="1"/>
+      <c r="AO36" s="1"/>
+    </row>
+    <row r="37" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1" t="s">
@@ -1702,8 +1992,33 @@
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S37" s="1"/>
+      <c r="T37" s="1"/>
+      <c r="U37" s="1"/>
+      <c r="V37" s="1"/>
+      <c r="W37" s="1"/>
+      <c r="X37" s="1"/>
+      <c r="Y37" s="1"/>
+      <c r="Z37" s="1"/>
+      <c r="AA37" s="1"/>
+      <c r="AB37" s="1"/>
+      <c r="AC37" s="1"/>
+      <c r="AD37" s="1"/>
+      <c r="AE37" s="1"/>
+      <c r="AF37" s="1"/>
+      <c r="AG37" s="1"/>
+      <c r="AH37" s="1"/>
+      <c r="AI37" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ37" s="1"/>
+      <c r="AK37" s="1"/>
+      <c r="AL37" s="1"/>
+      <c r="AM37" s="1"/>
+      <c r="AN37" s="1"/>
+      <c r="AO37" s="1"/>
+    </row>
+    <row r="38" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1" t="s">
@@ -1736,8 +2051,31 @@
       <c r="P38" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S38" s="1"/>
+      <c r="T38" s="1"/>
+      <c r="U38" s="1"/>
+      <c r="V38" s="1"/>
+      <c r="W38" s="1"/>
+      <c r="X38" s="1"/>
+      <c r="Y38" s="1"/>
+      <c r="Z38" s="1"/>
+      <c r="AA38" s="1"/>
+      <c r="AB38" s="1"/>
+      <c r="AC38" s="1"/>
+      <c r="AD38" s="1"/>
+      <c r="AE38" s="1"/>
+      <c r="AF38" s="1"/>
+      <c r="AG38" s="1"/>
+      <c r="AH38" s="1"/>
+      <c r="AI38" s="1"/>
+      <c r="AJ38" s="1"/>
+      <c r="AK38" s="1"/>
+      <c r="AL38" s="1"/>
+      <c r="AM38" s="1"/>
+      <c r="AN38" s="1"/>
+      <c r="AO38" s="1"/>
+    </row>
+    <row r="39" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1" t="s">
@@ -1762,8 +2100,46 @@
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="T39" s="1"/>
+      <c r="U39" s="1"/>
+      <c r="V39" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W39" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X39" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y39" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z39" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA39" s="1"/>
+      <c r="AB39" s="1"/>
+      <c r="AC39" s="1"/>
+      <c r="AD39" s="1"/>
+      <c r="AE39" s="1"/>
+      <c r="AF39" s="1"/>
+      <c r="AG39" s="1"/>
+      <c r="AH39" s="1"/>
+      <c r="AI39" s="1"/>
+      <c r="AJ39" s="1"/>
+      <c r="AK39" s="1"/>
+      <c r="AL39" s="1"/>
+      <c r="AM39" s="1"/>
+      <c r="AN39" s="1"/>
+      <c r="AO39" s="1"/>
+      <c r="AP39" s="1"/>
+      <c r="AQ39" s="1"/>
+      <c r="AR39" s="1"/>
+    </row>
+    <row r="40" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1" t="s">
@@ -1784,8 +2160,42 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S40" s="1"/>
+      <c r="T40" s="1">
+        <v>17</v>
+      </c>
+      <c r="U40" s="1"/>
+      <c r="V40" s="1"/>
+      <c r="W40" s="1"/>
+      <c r="X40" s="1"/>
+      <c r="Y40" s="1"/>
+      <c r="Z40" s="1"/>
+      <c r="AA40" s="1"/>
+      <c r="AB40" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC40" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD40" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE40" s="1"/>
+      <c r="AF40" s="1"/>
+      <c r="AG40" s="1"/>
+      <c r="AH40" s="1"/>
+      <c r="AI40" s="1"/>
+      <c r="AJ40" s="1"/>
+      <c r="AK40" s="1"/>
+      <c r="AL40" s="1"/>
+      <c r="AM40" s="1"/>
+      <c r="AN40" s="1"/>
+      <c r="AO40" s="1"/>
+      <c r="AP40" s="1"/>
+      <c r="AQ40" s="1"/>
+      <c r="AR40" s="1"/>
+    </row>
+    <row r="41" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1" t="s">
@@ -1806,8 +2216,36 @@
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S41" s="1"/>
+      <c r="T41" s="1"/>
+      <c r="U41" s="1">
+        <v>17</v>
+      </c>
+      <c r="V41" s="1"/>
+      <c r="W41" s="1"/>
+      <c r="X41" s="1"/>
+      <c r="Y41" s="1"/>
+      <c r="Z41" s="1"/>
+      <c r="AA41" s="1"/>
+      <c r="AB41" s="1"/>
+      <c r="AC41" s="1"/>
+      <c r="AD41" s="1"/>
+      <c r="AE41" s="1"/>
+      <c r="AF41" s="1"/>
+      <c r="AG41" s="1"/>
+      <c r="AH41" s="1"/>
+      <c r="AI41" s="1"/>
+      <c r="AJ41" s="1"/>
+      <c r="AK41" s="1"/>
+      <c r="AL41" s="1"/>
+      <c r="AM41" s="1"/>
+      <c r="AN41" s="1"/>
+      <c r="AO41" s="1"/>
+      <c r="AP41" s="1"/>
+      <c r="AQ41" s="1"/>
+      <c r="AR41" s="1"/>
+    </row>
+    <row r="42" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1" t="s">
@@ -1832,8 +2270,38 @@
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S42" s="1"/>
+      <c r="T42" s="1"/>
+      <c r="U42" s="1"/>
+      <c r="V42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W42" s="1"/>
+      <c r="X42" s="1"/>
+      <c r="Y42" s="1"/>
+      <c r="Z42" s="1"/>
+      <c r="AA42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB42" s="1"/>
+      <c r="AC42" s="1"/>
+      <c r="AD42" s="1"/>
+      <c r="AE42" s="1"/>
+      <c r="AF42" s="1"/>
+      <c r="AG42" s="1"/>
+      <c r="AH42" s="1"/>
+      <c r="AI42" s="1"/>
+      <c r="AJ42" s="1"/>
+      <c r="AK42" s="1"/>
+      <c r="AL42" s="1"/>
+      <c r="AM42" s="1"/>
+      <c r="AN42" s="1"/>
+      <c r="AO42" s="1"/>
+      <c r="AP42" s="1"/>
+      <c r="AQ42" s="1"/>
+      <c r="AR42" s="1"/>
+    </row>
+    <row r="43" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1" t="s">
@@ -1862,8 +2330,38 @@
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S43" s="1"/>
+      <c r="T43" s="1"/>
+      <c r="U43" s="1"/>
+      <c r="V43" s="1"/>
+      <c r="W43" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="X43" s="1"/>
+      <c r="Y43" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z43" s="1"/>
+      <c r="AA43" s="1"/>
+      <c r="AB43" s="1"/>
+      <c r="AC43" s="1"/>
+      <c r="AD43" s="1"/>
+      <c r="AE43" s="1"/>
+      <c r="AF43" s="1"/>
+      <c r="AG43" s="1"/>
+      <c r="AH43" s="1"/>
+      <c r="AI43" s="1"/>
+      <c r="AJ43" s="1"/>
+      <c r="AK43" s="1"/>
+      <c r="AL43" s="1"/>
+      <c r="AM43" s="1"/>
+      <c r="AN43" s="1"/>
+      <c r="AO43" s="1"/>
+      <c r="AP43" s="1"/>
+      <c r="AQ43" s="1"/>
+      <c r="AR43" s="1"/>
+    </row>
+    <row r="44" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1" t="s">
@@ -1884,8 +2382,38 @@
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S44" s="1"/>
+      <c r="T44" s="1"/>
+      <c r="U44" s="1"/>
+      <c r="V44" s="1"/>
+      <c r="W44" s="1"/>
+      <c r="X44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y44" s="1"/>
+      <c r="Z44" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA44" s="1"/>
+      <c r="AB44" s="1"/>
+      <c r="AC44" s="1"/>
+      <c r="AD44" s="1"/>
+      <c r="AE44" s="1"/>
+      <c r="AF44" s="1"/>
+      <c r="AG44" s="1"/>
+      <c r="AH44" s="1"/>
+      <c r="AI44" s="1"/>
+      <c r="AJ44" s="1"/>
+      <c r="AK44" s="1"/>
+      <c r="AL44" s="1"/>
+      <c r="AM44" s="1"/>
+      <c r="AN44" s="1"/>
+      <c r="AO44" s="1"/>
+      <c r="AP44" s="1"/>
+      <c r="AQ44" s="1"/>
+      <c r="AR44" s="1"/>
+    </row>
+    <row r="45" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1" t="s">
@@ -1906,8 +2434,34 @@
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S45" s="1"/>
+      <c r="T45" s="1"/>
+      <c r="U45" s="1"/>
+      <c r="V45" s="1"/>
+      <c r="W45" s="1"/>
+      <c r="X45" s="1"/>
+      <c r="Y45" s="1"/>
+      <c r="Z45" s="1"/>
+      <c r="AA45" s="1"/>
+      <c r="AB45" s="1"/>
+      <c r="AC45" s="1"/>
+      <c r="AD45" s="1"/>
+      <c r="AE45" s="1"/>
+      <c r="AF45" s="1"/>
+      <c r="AG45" s="1"/>
+      <c r="AH45" s="1"/>
+      <c r="AI45" s="1"/>
+      <c r="AJ45" s="1"/>
+      <c r="AK45" s="1"/>
+      <c r="AL45" s="1"/>
+      <c r="AM45" s="1"/>
+      <c r="AN45" s="1"/>
+      <c r="AO45" s="1"/>
+      <c r="AP45" s="1"/>
+      <c r="AQ45" s="1"/>
+      <c r="AR45" s="1"/>
+    </row>
+    <row r="46" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1" t="s">
@@ -1932,8 +2486,34 @@
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S46" s="1"/>
+      <c r="T46" s="1"/>
+      <c r="U46" s="1"/>
+      <c r="V46" s="1"/>
+      <c r="W46" s="1"/>
+      <c r="X46" s="1"/>
+      <c r="Y46" s="1"/>
+      <c r="Z46" s="1"/>
+      <c r="AA46" s="1"/>
+      <c r="AB46" s="1"/>
+      <c r="AC46" s="1"/>
+      <c r="AD46" s="1"/>
+      <c r="AE46" s="1"/>
+      <c r="AF46" s="1"/>
+      <c r="AG46" s="1"/>
+      <c r="AH46" s="1"/>
+      <c r="AI46" s="1"/>
+      <c r="AJ46" s="1"/>
+      <c r="AK46" s="1"/>
+      <c r="AL46" s="1"/>
+      <c r="AM46" s="1"/>
+      <c r="AN46" s="1"/>
+      <c r="AO46" s="1"/>
+      <c r="AP46" s="1"/>
+      <c r="AQ46" s="1"/>
+      <c r="AR46" s="1"/>
+    </row>
+    <row r="47" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -1950,8 +2530,34 @@
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S47" s="1"/>
+      <c r="T47" s="1"/>
+      <c r="U47" s="1"/>
+      <c r="V47" s="1"/>
+      <c r="W47" s="1"/>
+      <c r="X47" s="1"/>
+      <c r="Y47" s="1"/>
+      <c r="Z47" s="1"/>
+      <c r="AA47" s="1"/>
+      <c r="AB47" s="1"/>
+      <c r="AC47" s="1"/>
+      <c r="AD47" s="1"/>
+      <c r="AE47" s="1"/>
+      <c r="AF47" s="1"/>
+      <c r="AG47" s="1"/>
+      <c r="AH47" s="1"/>
+      <c r="AI47" s="1"/>
+      <c r="AJ47" s="1"/>
+      <c r="AK47" s="1"/>
+      <c r="AL47" s="1"/>
+      <c r="AM47" s="1"/>
+      <c r="AN47" s="1"/>
+      <c r="AO47" s="1"/>
+      <c r="AP47" s="1"/>
+      <c r="AQ47" s="1"/>
+      <c r="AR47" s="1"/>
+    </row>
+    <row r="48" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1" t="s">
         <v>16</v>
@@ -1972,6 +2578,32 @@
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="1"/>
+      <c r="U48" s="1"/>
+      <c r="V48" s="1"/>
+      <c r="W48" s="1"/>
+      <c r="X48" s="1"/>
+      <c r="Y48" s="1"/>
+      <c r="Z48" s="1"/>
+      <c r="AA48" s="1"/>
+      <c r="AB48" s="1"/>
+      <c r="AC48" s="1"/>
+      <c r="AD48" s="1"/>
+      <c r="AE48" s="1"/>
+      <c r="AF48" s="1"/>
+      <c r="AG48" s="1"/>
+      <c r="AH48" s="1"/>
+      <c r="AI48" s="1"/>
+      <c r="AJ48" s="1"/>
+      <c r="AK48" s="1"/>
+      <c r="AL48" s="1"/>
+      <c r="AM48" s="1"/>
+      <c r="AN48" s="1"/>
+      <c r="AO48" s="1"/>
+      <c r="AP48" s="1"/>
+      <c r="AQ48" s="1"/>
+      <c r="AR48" s="1"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
@@ -5890,5 +6522,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>